--- a/ResourcesPK/Excel_Validation.xlsx
+++ b/ResourcesPK/Excel_Validation.xlsx
@@ -39,10 +39,10 @@
     <t>20006443</t>
   </si>
   <si>
-    <t>2027-06-17</t>
-  </si>
-  <si>
     <t>2027-06-27</t>
+  </si>
+  <si>
+    <t>2026-06-10</t>
   </si>
 </sst>
 </file>
@@ -407,10 +407,10 @@
         <v>10000</v>
       </c>
       <c r="D2" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="E2" s="3" t="s">
         <v>6</v>
-      </c>
-      <c r="E2" s="3" t="s">
-        <v>7</v>
       </c>
     </row>
   </sheetData>
